--- a/basedatos_partidas/salida/descompuestos/07.04.01.040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/07.04.01.040.xlsx
@@ -584,10 +584,10 @@
         <v>0.28</v>
       </c>
       <c r="G11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="12">
@@ -610,10 +610,10 @@
         <v>0.26</v>
       </c>
       <c r="G12" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="H12" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="13">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>43.71</v>
+        <v>43.98</v>
       </c>
     </row>
     <row r="15">
@@ -847,7 +847,7 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>55.18</v>
+        <v>55.45</v>
       </c>
       <c r="H25" t="n">
         <v>0.55</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="5" t="n">
-        <v>55.73</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
